--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedPatientvbPKBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedPatientvbPKBund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
